--- a/Libraries/Vehicle/Linkage/MacPherson/sm_car_data_Linkage_MacPherson.xlsx
+++ b/Libraries/Vehicle/Linkage/MacPherson/sm_car_data_Linkage_MacPherson.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28827"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\vtpVDG\Libraries\Vehicle\Linkage\MacPherson\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GIT\Others\smiller\ssvt_srcR22a\Libraries\Vehicle\Linkage\MacPherson\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0B0D5421-98A0-4A48-8569-B7337D776C1D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{97DD2ECB-2EFB-4AE8-BE41-7EF7EB726DDC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="30660" yWindow="1110" windowWidth="15330" windowHeight="13050" tabRatio="913" activeTab="1" xr2:uid="{ACF2BADA-AF40-4151-8377-863ED7ABEE94}"/>
+    <workbookView xWindow="31110" yWindow="1290" windowWidth="21600" windowHeight="11295" tabRatio="913" xr2:uid="{ACF2BADA-AF40-4151-8377-863ED7ABEE94}"/>
   </bookViews>
   <sheets>
     <sheet name="MacP_Sedan_HambaLG_f" sheetId="8" r:id="rId1"/>
